--- a/HigherEdu/Catalogue/integration-details.xlsx
+++ b/HigherEdu/Catalogue/integration-details.xlsx
@@ -20,17 +20,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Governance, Risk &amp; Compliance" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Student Administration'!$A$1:$I$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Learning &amp; Teaching'!$A$1:$I$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'HR &amp; Faculty Management'!$A$1:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Finance &amp; Resource Management'!$A$1:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Research Management'!$A$1:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Institutional Engagement'!$A$1:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Library &amp; Learning Support'!$A$1:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Enterprise Data &amp; Analytics'!$A$1:$I$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Student Services &amp; Wellbeing'!$A$1:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Facilities &amp; Campus Operations'!$A$1:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Governance, Risk &amp; Compliance'!$A$1:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Student Administration'!$A$1:$J$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Learning &amp; Teaching'!$A$1:$J$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'HR &amp; Faculty Management'!$A$1:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Finance &amp; Resource Management'!$A$1:$J$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Research Management'!$A$1:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Institutional Engagement'!$A$1:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Library &amp; Learning Support'!$A$1:$J$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Enterprise Data &amp; Analytics'!$A$1:$J$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Student Services &amp; Wellbeing'!$A$1:$J$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Facilities &amp; Campus Operations'!$A$1:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Governance, Risk &amp; Compliance'!$A$1:$J$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -475,6 +475,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -523,6 +524,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -570,6 +576,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -617,6 +628,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -664,6 +680,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -711,6 +732,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -758,6 +784,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -805,6 +836,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -852,6 +888,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -899,6 +940,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -946,6 +992,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -993,6 +1044,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1040,6 +1096,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1087,6 +1148,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1134,6 +1200,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1181,6 +1252,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1228,6 +1304,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Intermediate ETL process with data cleansing, enrichment, and staging requirements</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1275,6 +1356,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Basic ETL pipeline with direct mapping and flat-file exchange</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1322,6 +1408,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1369,6 +1460,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1416,6 +1512,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1463,6 +1564,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1510,6 +1616,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1557,9 +1668,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I23"/>
+  <autoFilter ref="A1:J23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1570,7 +1686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1582,6 +1698,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1630,6 +1747,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1677,6 +1799,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1724,6 +1851,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1771,6 +1903,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1818,6 +1955,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1865,6 +2007,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1912,6 +2059,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1959,6 +2111,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2006,6 +2163,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2053,6 +2215,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2100,6 +2267,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2147,6 +2319,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2194,6 +2371,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2241,6 +2423,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2288,6 +2475,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2335,9 +2527,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I16"/>
+  <autoFilter ref="A1:J16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2348,7 +2545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2360,6 +2557,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2408,6 +2606,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2455,6 +2658,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2502,6 +2710,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2549,6 +2762,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2596,6 +2814,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2643,6 +2866,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2690,6 +2918,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2737,6 +2970,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2784,6 +3022,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2831,6 +3074,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Large-scale ETL pipeline requiring complex transformations, deduplication, and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2878,6 +3126,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2925,6 +3178,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2972,9 +3230,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I13"/>
+  <autoFilter ref="A1:J13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2985,7 +3248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2997,6 +3260,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3045,6 +3309,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3092,6 +3361,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3139,6 +3413,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3186,6 +3465,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3233,6 +3517,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3280,6 +3569,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3327,6 +3621,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3374,6 +3673,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -3421,6 +3725,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -3468,6 +3777,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3515,6 +3829,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3562,6 +3881,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3609,6 +3933,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3656,6 +3985,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3703,6 +4037,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3750,6 +4089,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3797,6 +4141,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3844,6 +4193,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3891,6 +4245,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3938,6 +4297,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3985,9 +4349,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I21"/>
+  <autoFilter ref="A1:J21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3998,7 +4367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4010,6 +4379,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4058,6 +4428,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -4105,6 +4480,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -4152,6 +4532,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4199,6 +4584,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -4246,6 +4636,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -4293,6 +4688,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4340,6 +4740,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -4387,6 +4792,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -4434,6 +4844,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -4481,6 +4896,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4528,6 +4948,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -4575,6 +5000,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -4622,6 +5052,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -4669,6 +5104,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -4716,6 +5156,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -4763,9 +5208,14 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I16"/>
+  <autoFilter ref="A1:J16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4776,7 +5226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4788,6 +5238,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4836,6 +5287,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -4883,6 +5339,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -4930,6 +5391,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4977,6 +5443,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -5024,6 +5495,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -5071,6 +5547,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -5118,6 +5599,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -5165,6 +5651,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -5212,6 +5703,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -5259,6 +5755,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -5306,6 +5807,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -5353,6 +5859,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -5400,6 +5911,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -5447,6 +5963,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -5494,9 +6015,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I15"/>
+  <autoFilter ref="A1:J15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5507,7 +6033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5519,6 +6045,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5567,6 +6094,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -5614,6 +6146,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -5661,6 +6198,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -5708,6 +6250,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -5755,6 +6302,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -5802,6 +6354,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -5849,6 +6406,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -5896,6 +6458,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -5943,6 +6510,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -5990,6 +6562,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -6037,6 +6614,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -6084,6 +6666,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -6131,6 +6718,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -6178,6 +6770,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -6225,6 +6822,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -6272,9 +6874,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I16"/>
+  <autoFilter ref="A1:J16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6285,7 +6892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6297,6 +6904,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6345,6 +6953,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -6392,6 +7005,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -6439,6 +7057,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -6486,6 +7109,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -6533,6 +7161,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -6580,6 +7213,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -6627,6 +7265,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -6674,6 +7317,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -6721,6 +7369,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -6768,6 +7421,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -6815,6 +7473,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -6862,6 +7525,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -6909,6 +7577,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -6956,6 +7629,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -7003,6 +7681,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -7050,9 +7733,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I16"/>
+  <autoFilter ref="A1:J16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7063,7 +7751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7075,6 +7763,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7123,6 +7812,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -7170,6 +7864,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -7217,6 +7916,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -7264,6 +7968,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -7311,6 +8020,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -7358,6 +8072,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -7405,6 +8124,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -7452,6 +8176,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -7499,6 +8228,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -7546,6 +8280,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -7593,6 +8332,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -7640,9 +8384,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I12"/>
+  <autoFilter ref="A1:J12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7653,7 +8402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7665,6 +8414,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7713,6 +8463,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -7760,6 +8515,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Continuous change-data-capture replication with conflict resolution and consistency guarantees</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -7807,6 +8567,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Intermediate ETL process with data cleansing, enrichment, and staging requirements</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -7854,6 +8619,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Intermediate ETL process with data cleansing, enrichment, and staging requirements</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -7901,6 +8671,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Intermediate ETL process with data cleansing, enrichment, and staging requirements</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -7948,6 +8723,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Intermediate ETL process with data cleansing, enrichment, and staging requirements</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -7995,6 +8775,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -8042,6 +8827,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Intermediate ETL process with data cleansing, enrichment, and staging requirements</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -8089,6 +8879,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -8136,6 +8931,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -8183,6 +8983,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -8230,6 +9035,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -8277,6 +9087,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -8324,6 +9139,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -8371,6 +9191,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -8418,6 +9243,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Intermediate ETL process with data cleansing, enrichment, and staging requirements</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -8465,6 +9295,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -8512,9 +9347,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I18"/>
+  <autoFilter ref="A1:J18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8525,7 +9365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8537,6 +9377,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8585,6 +9426,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -8632,6 +9478,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -8679,6 +9530,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -8726,6 +9582,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -8773,6 +9634,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -8820,6 +9686,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -8867,6 +9738,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -8914,6 +9790,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -8961,6 +9842,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -9008,6 +9894,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -9055,6 +9946,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -9102,6 +9998,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -9149,9 +10050,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I13"/>
+  <autoFilter ref="A1:J13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>